--- a/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,25 +368,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1_cost</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_cost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3_cost</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -397,22 +407,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>119.36</v>
+        <v>119.3</v>
       </c>
       <c r="C2">
-        <v>96.18000000000001</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>84</v>
+        <v>96.03</v>
       </c>
       <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
         <v>168</v>
       </c>
-      <c r="G2">
-        <v>19299</v>
+      <c r="I2">
+        <v>19034</v>
       </c>
     </row>
     <row r="3">
@@ -420,22 +436,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>104.57</v>
+        <v>104.58</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>1164.77</v>
       </c>
       <c r="E3">
-        <v>84</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="F3">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>15876</v>
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>126</v>
+      </c>
+      <c r="I3">
+        <v>15872</v>
       </c>
     </row>
     <row r="4">
@@ -446,18 +468,24 @@
         <v>103.92</v>
       </c>
       <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1078.73</v>
+      </c>
+      <c r="E4">
         <v>87.92</v>
       </c>
-      <c r="D4">
-        <v>42</v>
-      </c>
-      <c r="E4">
-        <v>84</v>
-      </c>
       <c r="F4">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>126</v>
+      </c>
+      <c r="I4">
         <v>14615</v>
       </c>
     </row>
@@ -469,18 +497,24 @@
         <v>100.18</v>
       </c>
       <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>1302</v>
+      </c>
+      <c r="E5">
         <v>83.27</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>84</v>
-      </c>
       <c r="F5">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>126</v>
+      </c>
+      <c r="I5">
         <v>13625</v>
       </c>
     </row>
@@ -492,18 +526,24 @@
         <v>99.15000000000001</v>
       </c>
       <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>989.49</v>
+      </c>
+      <c r="E6">
         <v>83.15000000000001</v>
       </c>
-      <c r="D6">
-        <v>42</v>
-      </c>
-      <c r="E6">
-        <v>84</v>
-      </c>
       <c r="F6">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>126</v>
+      </c>
+      <c r="I6">
         <v>12723</v>
       </c>
     </row>
@@ -515,18 +555,24 @@
         <v>98.2</v>
       </c>
       <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1689.75</v>
+      </c>
+      <c r="E7">
         <v>83.37</v>
       </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>84</v>
-      </c>
       <c r="F7">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G7">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>126</v>
+      </c>
+      <c r="I7">
         <v>12233</v>
       </c>
     </row>
@@ -538,18 +584,24 @@
         <v>97.81</v>
       </c>
       <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1034.75</v>
+      </c>
+      <c r="E8">
         <v>81.59</v>
       </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>84</v>
-      </c>
       <c r="F8">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G8">
+        <v>84</v>
+      </c>
+      <c r="H8">
+        <v>126</v>
+      </c>
+      <c r="I8">
         <v>11695</v>
       </c>
     </row>
@@ -561,18 +613,24 @@
         <v>95.53</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>1214.24</v>
+      </c>
+      <c r="E9">
         <v>78.73999999999999</v>
       </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
       <c r="F9">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G9">
+        <v>84</v>
+      </c>
+      <c r="H9">
+        <v>126</v>
+      </c>
+      <c r="I9">
         <v>11347</v>
       </c>
     </row>
@@ -584,18 +642,24 @@
         <v>97.78</v>
       </c>
       <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>1344</v>
+      </c>
+      <c r="E10">
         <v>81.23999999999999</v>
       </c>
-      <c r="D10">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>84</v>
-      </c>
       <c r="F10">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
+        <v>126</v>
+      </c>
+      <c r="I10">
         <v>11155</v>
       </c>
     </row>
@@ -607,18 +671,24 @@
         <v>95.61</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>1382.24</v>
+      </c>
+      <c r="E11">
         <v>77.88</v>
       </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>84</v>
-      </c>
       <c r="F11">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G11">
+        <v>84</v>
+      </c>
+      <c r="H11">
+        <v>126</v>
+      </c>
+      <c r="I11">
         <v>10900</v>
       </c>
     </row>
@@ -630,18 +700,24 @@
         <v>95.31</v>
       </c>
       <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>1664.75</v>
+      </c>
+      <c r="E12">
         <v>77.87</v>
       </c>
-      <c r="D12">
-        <v>42</v>
-      </c>
-      <c r="E12">
-        <v>84</v>
-      </c>
       <c r="F12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
+        <v>126</v>
+      </c>
+      <c r="I12">
         <v>10696</v>
       </c>
     </row>
@@ -653,18 +729,24 @@
         <v>96.52</v>
       </c>
       <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>1282.98</v>
+      </c>
+      <c r="E13">
         <v>79.84999999999999</v>
       </c>
-      <c r="D13">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>84</v>
-      </c>
       <c r="F13">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G13">
+        <v>84</v>
+      </c>
+      <c r="H13">
+        <v>126</v>
+      </c>
+      <c r="I13">
         <v>10585</v>
       </c>
     </row>
@@ -676,18 +758,24 @@
         <v>96.13</v>
       </c>
       <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>872.33</v>
+      </c>
+      <c r="E14">
         <v>78.01000000000001</v>
       </c>
-      <c r="D14">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>84</v>
-      </c>
       <c r="F14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G14">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>126</v>
+      </c>
+      <c r="I14">
         <v>10438</v>
       </c>
     </row>
@@ -699,18 +787,24 @@
         <v>96.43000000000001</v>
       </c>
       <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1349.3</v>
+      </c>
+      <c r="E15">
         <v>79.09</v>
       </c>
-      <c r="D15">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>84</v>
-      </c>
       <c r="F15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G15">
+        <v>84</v>
+      </c>
+      <c r="H15">
+        <v>126</v>
+      </c>
+      <c r="I15">
         <v>10096</v>
       </c>
     </row>
@@ -722,18 +816,24 @@
         <v>97.55</v>
       </c>
       <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>856.77</v>
+      </c>
+      <c r="E16">
         <v>81.12</v>
       </c>
-      <c r="D16">
-        <v>42</v>
-      </c>
-      <c r="E16">
-        <v>84</v>
-      </c>
       <c r="F16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G16">
+        <v>84</v>
+      </c>
+      <c r="H16">
+        <v>126</v>
+      </c>
+      <c r="I16">
         <v>9940</v>
       </c>
     </row>
@@ -745,18 +845,24 @@
         <v>95.62</v>
       </c>
       <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>954.71</v>
+      </c>
+      <c r="E17">
         <v>79.81</v>
       </c>
-      <c r="D17">
-        <v>42</v>
-      </c>
-      <c r="E17">
-        <v>84</v>
-      </c>
       <c r="F17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G17">
+        <v>84</v>
+      </c>
+      <c r="H17">
+        <v>126</v>
+      </c>
+      <c r="I17">
         <v>9820</v>
       </c>
     </row>
@@ -768,18 +874,24 @@
         <v>96.20999999999999</v>
       </c>
       <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>1154.89</v>
+      </c>
+      <c r="E18">
         <v>78.44</v>
       </c>
-      <c r="D18">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>84</v>
-      </c>
       <c r="F18">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G18">
+        <v>84</v>
+      </c>
+      <c r="H18">
+        <v>126</v>
+      </c>
+      <c r="I18">
         <v>9735</v>
       </c>
     </row>
@@ -791,18 +903,24 @@
         <v>96.44</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>894.67</v>
+      </c>
+      <c r="E19">
         <v>80.70999999999999</v>
       </c>
-      <c r="D19">
-        <v>42</v>
-      </c>
-      <c r="E19">
-        <v>84</v>
-      </c>
       <c r="F19">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G19">
+        <v>84</v>
+      </c>
+      <c r="H19">
+        <v>126</v>
+      </c>
+      <c r="I19">
         <v>9606</v>
       </c>
     </row>
@@ -814,18 +932,24 @@
         <v>95.09</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>739.78</v>
+      </c>
+      <c r="E20">
         <v>77.88</v>
       </c>
-      <c r="D20">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>84</v>
-      </c>
       <c r="F20">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>126</v>
+      </c>
+      <c r="I20">
         <v>9591</v>
       </c>
     </row>
@@ -837,18 +961,24 @@
         <v>96.06</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>842</v>
+      </c>
+      <c r="E21">
         <v>78.73</v>
       </c>
-      <c r="D21">
-        <v>42</v>
-      </c>
-      <c r="E21">
-        <v>84</v>
-      </c>
       <c r="F21">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G21">
+        <v>84</v>
+      </c>
+      <c r="H21">
+        <v>126</v>
+      </c>
+      <c r="I21">
         <v>9411</v>
       </c>
     </row>
@@ -860,18 +990,24 @@
         <v>95.86</v>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>908</v>
+      </c>
+      <c r="E22">
         <v>79.52</v>
       </c>
-      <c r="D22">
-        <v>42</v>
-      </c>
-      <c r="E22">
-        <v>84</v>
-      </c>
       <c r="F22">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G22">
+        <v>84</v>
+      </c>
+      <c r="H22">
+        <v>126</v>
+      </c>
+      <c r="I22">
         <v>9332</v>
       </c>
     </row>
@@ -883,18 +1019,24 @@
         <v>95.34</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>1028.35</v>
+      </c>
+      <c r="E23">
         <v>78.20999999999999</v>
       </c>
-      <c r="D23">
-        <v>42</v>
-      </c>
-      <c r="E23">
-        <v>84</v>
-      </c>
       <c r="F23">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G23">
+        <v>84</v>
+      </c>
+      <c r="H23">
+        <v>126</v>
+      </c>
+      <c r="I23">
         <v>9113</v>
       </c>
     </row>
@@ -906,18 +1048,24 @@
         <v>95.20999999999999</v>
       </c>
       <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>897.45</v>
+      </c>
+      <c r="E24">
         <v>77.84999999999999</v>
       </c>
-      <c r="D24">
-        <v>42</v>
-      </c>
-      <c r="E24">
-        <v>84</v>
-      </c>
       <c r="F24">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G24">
+        <v>84</v>
+      </c>
+      <c r="H24">
+        <v>126</v>
+      </c>
+      <c r="I24">
         <v>9107</v>
       </c>
     </row>
@@ -929,18 +1077,24 @@
         <v>95.06999999999999</v>
       </c>
       <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>782.75</v>
+      </c>
+      <c r="E25">
         <v>77.66</v>
       </c>
-      <c r="D25">
-        <v>42</v>
-      </c>
-      <c r="E25">
-        <v>84</v>
-      </c>
       <c r="F25">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G25">
+        <v>84</v>
+      </c>
+      <c r="H25">
+        <v>126</v>
+      </c>
+      <c r="I25">
         <v>8906</v>
       </c>
     </row>
@@ -952,18 +1106,24 @@
         <v>42.24</v>
       </c>
       <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26">
+        <v>115.72</v>
+      </c>
+      <c r="E26">
         <v>12.47</v>
       </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>42</v>
-      </c>
       <c r="F26">
         <v>42</v>
       </c>
       <c r="G26">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>42</v>
+      </c>
+      <c r="I26">
         <v>405</v>
       </c>
     </row>
@@ -974,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -990,25 +1150,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_cost</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1_cost</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median_cost</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3_cost</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -1019,22 +1189,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>119.43</v>
+        <v>119.3</v>
       </c>
       <c r="C2">
-        <v>96.2</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>84</v>
+        <v>96.03</v>
       </c>
       <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>84</v>
+      </c>
+      <c r="H2">
         <v>168</v>
       </c>
-      <c r="G2">
-        <v>19193</v>
+      <c r="I2">
+        <v>19034</v>
       </c>
     </row>
     <row r="3">
@@ -1045,18 +1221,24 @@
         <v>104.71</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1164.77</v>
+      </c>
+      <c r="E3">
         <v>89.09</v>
       </c>
-      <c r="D3">
-        <v>42</v>
-      </c>
-      <c r="E3">
-        <v>84</v>
-      </c>
       <c r="F3">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>126</v>
+      </c>
+      <c r="I3">
         <v>15793</v>
       </c>
     </row>
@@ -1068,18 +1250,24 @@
         <v>104.03</v>
       </c>
       <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1078.73</v>
+      </c>
+      <c r="E4">
         <v>88.01000000000001</v>
       </c>
-      <c r="D4">
-        <v>42</v>
-      </c>
-      <c r="E4">
-        <v>84</v>
-      </c>
       <c r="F4">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>126</v>
+      </c>
+      <c r="I4">
         <v>14544</v>
       </c>
     </row>
@@ -1091,18 +1279,24 @@
         <v>100.54</v>
       </c>
       <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>1302</v>
+      </c>
+      <c r="E5">
         <v>83.42</v>
       </c>
-      <c r="D5">
-        <v>42</v>
-      </c>
-      <c r="E5">
-        <v>84</v>
-      </c>
       <c r="F5">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>126</v>
+      </c>
+      <c r="I5">
         <v>13433</v>
       </c>
     </row>
@@ -1114,18 +1308,24 @@
         <v>99.39</v>
       </c>
       <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>989.49</v>
+      </c>
+      <c r="E6">
         <v>83.25</v>
       </c>
-      <c r="D6">
-        <v>42</v>
-      </c>
-      <c r="E6">
-        <v>84</v>
-      </c>
       <c r="F6">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G6">
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>126</v>
+      </c>
+      <c r="I6">
         <v>12599</v>
       </c>
     </row>
@@ -1137,18 +1337,24 @@
         <v>98.44</v>
       </c>
       <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>1689.75</v>
+      </c>
+      <c r="E7">
         <v>83.55</v>
       </c>
-      <c r="D7">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>84</v>
-      </c>
       <c r="F7">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G7">
+        <v>84</v>
+      </c>
+      <c r="H7">
+        <v>126</v>
+      </c>
+      <c r="I7">
         <v>12120</v>
       </c>
     </row>
@@ -1160,18 +1366,24 @@
         <v>97.91</v>
       </c>
       <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>1034.75</v>
+      </c>
+      <c r="E8">
         <v>81.69</v>
       </c>
-      <c r="D8">
-        <v>42</v>
-      </c>
-      <c r="E8">
-        <v>84</v>
-      </c>
       <c r="F8">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G8">
+        <v>84</v>
+      </c>
+      <c r="H8">
+        <v>126</v>
+      </c>
+      <c r="I8">
         <v>11620</v>
       </c>
     </row>
@@ -1183,18 +1395,24 @@
         <v>95.68000000000001</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>1214.24</v>
+      </c>
+      <c r="E9">
         <v>78.86</v>
       </c>
-      <c r="D9">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>84</v>
-      </c>
       <c r="F9">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G9">
+        <v>84</v>
+      </c>
+      <c r="H9">
+        <v>126</v>
+      </c>
+      <c r="I9">
         <v>11261</v>
       </c>
     </row>
@@ -1206,18 +1424,24 @@
         <v>97.87</v>
       </c>
       <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>1344</v>
+      </c>
+      <c r="E10">
         <v>81.31</v>
       </c>
-      <c r="D10">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>84</v>
-      </c>
       <c r="F10">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G10">
+        <v>84</v>
+      </c>
+      <c r="H10">
+        <v>126</v>
+      </c>
+      <c r="I10">
         <v>11084</v>
       </c>
     </row>
@@ -1229,18 +1453,24 @@
         <v>95.75</v>
       </c>
       <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>1382.24</v>
+      </c>
+      <c r="E11">
         <v>77.92</v>
       </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11">
-        <v>84</v>
-      </c>
       <c r="F11">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G11">
+        <v>84</v>
+      </c>
+      <c r="H11">
+        <v>126</v>
+      </c>
+      <c r="I11">
         <v>10842</v>
       </c>
     </row>
@@ -1252,18 +1482,24 @@
         <v>95.43000000000001</v>
       </c>
       <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>1664.75</v>
+      </c>
+      <c r="E12">
         <v>77.95999999999999</v>
       </c>
-      <c r="D12">
-        <v>42</v>
-      </c>
-      <c r="E12">
-        <v>84</v>
-      </c>
       <c r="F12">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
+        <v>126</v>
+      </c>
+      <c r="I12">
         <v>10638</v>
       </c>
     </row>
@@ -1275,18 +1511,24 @@
         <v>96.52</v>
       </c>
       <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>1282.98</v>
+      </c>
+      <c r="E13">
         <v>79.73999999999999</v>
       </c>
-      <c r="D13">
-        <v>42</v>
-      </c>
-      <c r="E13">
-        <v>84</v>
-      </c>
       <c r="F13">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G13">
+        <v>84</v>
+      </c>
+      <c r="H13">
+        <v>126</v>
+      </c>
+      <c r="I13">
         <v>10523</v>
       </c>
     </row>
@@ -1298,18 +1540,24 @@
         <v>96.19</v>
       </c>
       <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>872.33</v>
+      </c>
+      <c r="E14">
         <v>78.08</v>
       </c>
-      <c r="D14">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>84</v>
-      </c>
       <c r="F14">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G14">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>126</v>
+      </c>
+      <c r="I14">
         <v>10386</v>
       </c>
     </row>
@@ -1321,18 +1569,24 @@
         <v>96.47</v>
       </c>
       <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>1349.3</v>
+      </c>
+      <c r="E15">
         <v>79.17</v>
       </c>
-      <c r="D15">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>84</v>
-      </c>
       <c r="F15">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G15">
+        <v>84</v>
+      </c>
+      <c r="H15">
+        <v>126</v>
+      </c>
+      <c r="I15">
         <v>10054</v>
       </c>
     </row>
@@ -1344,18 +1598,24 @@
         <v>97.58</v>
       </c>
       <c r="C16">
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>856.77</v>
+      </c>
+      <c r="E16">
         <v>81.14</v>
       </c>
-      <c r="D16">
-        <v>42</v>
-      </c>
-      <c r="E16">
-        <v>84</v>
-      </c>
       <c r="F16">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G16">
+        <v>84</v>
+      </c>
+      <c r="H16">
+        <v>126</v>
+      </c>
+      <c r="I16">
         <v>9895</v>
       </c>
     </row>
@@ -1367,18 +1627,24 @@
         <v>95.7</v>
       </c>
       <c r="C17">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>954.71</v>
+      </c>
+      <c r="E17">
         <v>79.8</v>
       </c>
-      <c r="D17">
-        <v>42</v>
-      </c>
-      <c r="E17">
-        <v>84</v>
-      </c>
       <c r="F17">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G17">
+        <v>84</v>
+      </c>
+      <c r="H17">
+        <v>126</v>
+      </c>
+      <c r="I17">
         <v>9771</v>
       </c>
     </row>
@@ -1390,18 +1656,24 @@
         <v>96.25</v>
       </c>
       <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>1154.89</v>
+      </c>
+      <c r="E18">
         <v>78.40000000000001</v>
       </c>
-      <c r="D18">
-        <v>42</v>
-      </c>
-      <c r="E18">
-        <v>84</v>
-      </c>
       <c r="F18">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G18">
+        <v>84</v>
+      </c>
+      <c r="H18">
+        <v>126</v>
+      </c>
+      <c r="I18">
         <v>9692</v>
       </c>
     </row>
@@ -1413,18 +1685,24 @@
         <v>96.48999999999999</v>
       </c>
       <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19">
+        <v>894.67</v>
+      </c>
+      <c r="E19">
         <v>80.77</v>
       </c>
-      <c r="D19">
-        <v>42</v>
-      </c>
-      <c r="E19">
-        <v>84</v>
-      </c>
       <c r="F19">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G19">
+        <v>84</v>
+      </c>
+      <c r="H19">
+        <v>126</v>
+      </c>
+      <c r="I19">
         <v>9561</v>
       </c>
     </row>
@@ -1436,18 +1714,24 @@
         <v>95.11</v>
       </c>
       <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>739.78</v>
+      </c>
+      <c r="E20">
         <v>77.91</v>
       </c>
-      <c r="D20">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>84</v>
-      </c>
       <c r="F20">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>126</v>
+      </c>
+      <c r="I20">
         <v>9552</v>
       </c>
     </row>
@@ -1459,18 +1743,24 @@
         <v>96.03</v>
       </c>
       <c r="C21">
+        <v>6</v>
+      </c>
+      <c r="D21">
+        <v>842</v>
+      </c>
+      <c r="E21">
         <v>78.72</v>
       </c>
-      <c r="D21">
-        <v>42</v>
-      </c>
-      <c r="E21">
-        <v>84</v>
-      </c>
       <c r="F21">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G21">
+        <v>84</v>
+      </c>
+      <c r="H21">
+        <v>126</v>
+      </c>
+      <c r="I21">
         <v>9369</v>
       </c>
     </row>
@@ -1482,18 +1772,24 @@
         <v>95.88</v>
       </c>
       <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>882</v>
+      </c>
+      <c r="E22">
         <v>79.18000000000001</v>
       </c>
-      <c r="D22">
-        <v>42</v>
-      </c>
-      <c r="E22">
-        <v>84</v>
-      </c>
       <c r="F22">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G22">
+        <v>84</v>
+      </c>
+      <c r="H22">
+        <v>126</v>
+      </c>
+      <c r="I22">
         <v>9293</v>
       </c>
     </row>
@@ -1505,18 +1801,24 @@
         <v>95.38</v>
       </c>
       <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>1028.35</v>
+      </c>
+      <c r="E23">
         <v>78.31999999999999</v>
       </c>
-      <c r="D23">
-        <v>42</v>
-      </c>
-      <c r="E23">
-        <v>84</v>
-      </c>
       <c r="F23">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G23">
+        <v>84</v>
+      </c>
+      <c r="H23">
+        <v>126</v>
+      </c>
+      <c r="I23">
         <v>9066</v>
       </c>
     </row>
@@ -1528,18 +1830,24 @@
         <v>95.28</v>
       </c>
       <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>897.45</v>
+      </c>
+      <c r="E24">
         <v>77.86</v>
       </c>
-      <c r="D24">
-        <v>42</v>
-      </c>
-      <c r="E24">
-        <v>84</v>
-      </c>
       <c r="F24">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G24">
+        <v>84</v>
+      </c>
+      <c r="H24">
+        <v>126</v>
+      </c>
+      <c r="I24">
         <v>9079</v>
       </c>
     </row>
@@ -1551,18 +1859,24 @@
         <v>95.15000000000001</v>
       </c>
       <c r="C25">
+        <v>6</v>
+      </c>
+      <c r="D25">
+        <v>782.75</v>
+      </c>
+      <c r="E25">
         <v>77.73999999999999</v>
       </c>
-      <c r="D25">
-        <v>42</v>
-      </c>
-      <c r="E25">
-        <v>84</v>
-      </c>
       <c r="F25">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="G25">
+        <v>84</v>
+      </c>
+      <c r="H25">
+        <v>126</v>
+      </c>
+      <c r="I25">
         <v>8866</v>
       </c>
     </row>
@@ -1574,18 +1888,24 @@
         <v>39.47</v>
       </c>
       <c r="C26">
+        <v>19.2</v>
+      </c>
+      <c r="D26">
+        <v>42</v>
+      </c>
+      <c r="E26">
         <v>7.6</v>
       </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>42</v>
-      </c>
       <c r="F26">
         <v>42</v>
       </c>
       <c r="G26">
+        <v>42</v>
+      </c>
+      <c r="H26">
+        <v>42</v>
+      </c>
+      <c r="I26">
         <v>9</v>
       </c>
     </row>

--- a/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,10 +404,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>119.3</v>
+        <v>120.55</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -416,7 +416,7 @@
         <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>96.03</v>
+        <v>97.52</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -428,15 +428,15 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>19034</v>
+        <v>19110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>104.58</v>
+        <v>103.77</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -445,7 +445,7 @@
         <v>1164.77</v>
       </c>
       <c r="E3">
-        <v>89.01000000000001</v>
+        <v>88.14</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -457,15 +457,15 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>15872</v>
+        <v>15773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>103.92</v>
+        <v>105.04</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -474,7 +474,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>87.92</v>
+        <v>89</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -486,24 +486,24 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>14615</v>
+        <v>14724</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>100.18</v>
+        <v>99.3</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1302</v>
+        <v>1260</v>
       </c>
       <c r="E5">
-        <v>83.27</v>
+        <v>82.08</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -515,15 +515,15 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>13625</v>
+        <v>13502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>99.15000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -532,7 +532,7 @@
         <v>989.49</v>
       </c>
       <c r="E6">
-        <v>83.15000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -544,15 +544,15 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>12723</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>98.2</v>
+        <v>97.63</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -561,7 +561,7 @@
         <v>1689.75</v>
       </c>
       <c r="E7">
-        <v>83.37</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -573,24 +573,24 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>12233</v>
+        <v>12157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>97.81</v>
+        <v>98.62</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1034.75</v>
+        <v>1076.75</v>
       </c>
       <c r="E8">
-        <v>81.59</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -602,15 +602,15 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>11695</v>
+        <v>11772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>95.53</v>
+        <v>94.98</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -619,7 +619,7 @@
         <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>78.73999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="F9">
         <v>42</v>
@@ -631,24 +631,24 @@
         <v>126</v>
       </c>
       <c r="I9">
-        <v>11347</v>
+        <v>11232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>97.78</v>
+        <v>97</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1344</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>81.23999999999999</v>
+        <v>80.83</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -660,24 +660,24 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>11155</v>
+        <v>11129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>95.61</v>
+        <v>96.3</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>1382.24</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>77.88</v>
+        <v>78.39</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -689,24 +689,24 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>10900</v>
+        <v>10982</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>95.31</v>
+        <v>94.7</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>1664.75</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>77.87</v>
+        <v>77.27</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -718,24 +718,24 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>10696</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>96.52</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>1282.98</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>79.84999999999999</v>
+        <v>81.03</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -747,24 +747,24 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>10585</v>
+        <v>10692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>96.13</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>872.33</v>
+        <v>853.1799999999999</v>
       </c>
       <c r="E14">
-        <v>78.01000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -776,24 +776,24 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>10438</v>
+        <v>10348</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>96.43000000000001</v>
+        <v>97.31</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>1349.3</v>
+        <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>79.09</v>
+        <v>80.09</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -805,15 +805,15 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>10096</v>
+        <v>10184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>97.55</v>
+        <v>97.09</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -822,7 +822,7 @@
         <v>856.77</v>
       </c>
       <c r="E16">
-        <v>81.12</v>
+        <v>80.48</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -834,24 +834,24 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>9940</v>
+        <v>9852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>95.62</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>954.71</v>
+        <v>926</v>
       </c>
       <c r="E17">
-        <v>79.81</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="F17">
         <v>42</v>
@@ -863,15 +863,15 @@
         <v>126</v>
       </c>
       <c r="I17">
-        <v>9820</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>96.20999999999999</v>
+        <v>95.67</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -880,7 +880,7 @@
         <v>1154.89</v>
       </c>
       <c r="E18">
-        <v>78.44</v>
+        <v>77.97</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -892,15 +892,15 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>9735</v>
+        <v>9671</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>96.44</v>
+        <v>95.66</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -909,7 +909,7 @@
         <v>894.67</v>
       </c>
       <c r="E19">
-        <v>80.70999999999999</v>
+        <v>79.98</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -921,15 +921,15 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>9606</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>95.09</v>
+        <v>95.86</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -938,7 +938,7 @@
         <v>739.78</v>
       </c>
       <c r="E20">
-        <v>77.88</v>
+        <v>78.77</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -950,15 +950,15 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>9591</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>96.06</v>
+        <v>95.11</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -967,7 +967,7 @@
         <v>842</v>
       </c>
       <c r="E21">
-        <v>78.73</v>
+        <v>77.63</v>
       </c>
       <c r="F21">
         <v>42</v>
@@ -979,15 +979,15 @@
         <v>126</v>
       </c>
       <c r="I21">
-        <v>9411</v>
+        <v>9355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>95.86</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -996,7 +996,7 @@
         <v>908</v>
       </c>
       <c r="E22">
-        <v>79.52</v>
+        <v>80.88</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1008,15 +1008,15 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>9332</v>
+        <v>9422</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>95.34</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1025,7 +1025,7 @@
         <v>1028.35</v>
       </c>
       <c r="E23">
-        <v>78.20999999999999</v>
+        <v>77.31</v>
       </c>
       <c r="F23">
         <v>42</v>
@@ -1037,15 +1037,15 @@
         <v>126</v>
       </c>
       <c r="I23">
-        <v>9113</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>95.20999999999999</v>
+        <v>96.45</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1054,7 +1054,7 @@
         <v>897.45</v>
       </c>
       <c r="E24">
-        <v>77.84999999999999</v>
+        <v>78.81</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1066,24 +1066,24 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>9107</v>
+        <v>9230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>95.06999999999999</v>
+        <v>94.22</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25">
-        <v>782.75</v>
+        <v>756</v>
       </c>
       <c r="E25">
-        <v>77.66</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="F25">
         <v>42</v>
@@ -1095,36 +1095,7 @@
         <v>126</v>
       </c>
       <c r="I25">
-        <v>8906</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>42.24</v>
-      </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
-      <c r="D26">
-        <v>115.72</v>
-      </c>
-      <c r="E26">
-        <v>12.47</v>
-      </c>
-      <c r="F26">
-        <v>42</v>
-      </c>
-      <c r="G26">
-        <v>42</v>
-      </c>
-      <c r="H26">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>405</v>
+        <v>8767</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1186,10 +1157,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>119.3</v>
+        <v>120.55</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -1198,7 +1169,7 @@
         <v>1712.67</v>
       </c>
       <c r="E2">
-        <v>96.03</v>
+        <v>97.52</v>
       </c>
       <c r="F2">
         <v>42</v>
@@ -1210,15 +1181,15 @@
         <v>168</v>
       </c>
       <c r="I2">
-        <v>19034</v>
+        <v>19110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>104.71</v>
+        <v>103.76</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -1227,7 +1198,7 @@
         <v>1164.77</v>
       </c>
       <c r="E3">
-        <v>89.09</v>
+        <v>88.05</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -1239,15 +1210,15 @@
         <v>126</v>
       </c>
       <c r="I3">
-        <v>15793</v>
+        <v>15561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>104.03</v>
+        <v>105.03</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -1256,7 +1227,7 @@
         <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>88.01000000000001</v>
+        <v>88.86</v>
       </c>
       <c r="F4">
         <v>42</v>
@@ -1268,24 +1239,24 @@
         <v>126</v>
       </c>
       <c r="I4">
-        <v>14544</v>
+        <v>14529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>100.54</v>
+        <v>99.69</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>1302</v>
+        <v>1260</v>
       </c>
       <c r="E5">
-        <v>83.42</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -1297,15 +1268,15 @@
         <v>126</v>
       </c>
       <c r="I5">
-        <v>13433</v>
+        <v>13125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>99.39</v>
+        <v>100.14</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1314,7 +1285,7 @@
         <v>989.49</v>
       </c>
       <c r="E6">
-        <v>83.25</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="F6">
         <v>42</v>
@@ -1326,15 +1297,15 @@
         <v>126</v>
       </c>
       <c r="I6">
-        <v>12599</v>
+        <v>12545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>98.44</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1343,7 +1314,7 @@
         <v>1689.75</v>
       </c>
       <c r="E7">
-        <v>83.55</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="F7">
         <v>42</v>
@@ -1355,24 +1326,24 @@
         <v>126</v>
       </c>
       <c r="I7">
-        <v>12120</v>
+        <v>11939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>97.91</v>
+        <v>98.53</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1034.75</v>
+        <v>1076.75</v>
       </c>
       <c r="E8">
-        <v>81.69</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="F8">
         <v>42</v>
@@ -1384,15 +1355,15 @@
         <v>126</v>
       </c>
       <c r="I8">
-        <v>11620</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>95.68000000000001</v>
+        <v>94.94</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1401,7 +1372,7 @@
         <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>78.86</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="F9">
         <v>42</v>
@@ -1413,24 +1384,24 @@
         <v>126</v>
       </c>
       <c r="I9">
-        <v>11261</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>97.87</v>
+        <v>97.02</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>1344</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>81.31</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F10">
         <v>42</v>
@@ -1442,24 +1413,24 @@
         <v>126</v>
       </c>
       <c r="I10">
-        <v>11084</v>
+        <v>10977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>95.75</v>
+        <v>96.42</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>1382.24</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>77.92</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="F11">
         <v>42</v>
@@ -1471,24 +1442,24 @@
         <v>126</v>
       </c>
       <c r="I11">
-        <v>10842</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>95.43000000000001</v>
+        <v>94.77</v>
       </c>
       <c r="C12">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>1664.75</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>77.95999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="F12">
         <v>42</v>
@@ -1500,24 +1471,24 @@
         <v>126</v>
       </c>
       <c r="I12">
-        <v>10638</v>
+        <v>10496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>96.52</v>
+        <v>97.59</v>
       </c>
       <c r="C13">
         <v>6</v>
       </c>
       <c r="D13">
-        <v>1282.98</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>79.73999999999999</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="F13">
         <v>42</v>
@@ -1529,24 +1500,24 @@
         <v>126</v>
       </c>
       <c r="I13">
-        <v>10523</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>96.19</v>
+        <v>95.27</v>
       </c>
       <c r="C14">
         <v>6</v>
       </c>
       <c r="D14">
-        <v>872.33</v>
+        <v>853.1799999999999</v>
       </c>
       <c r="E14">
-        <v>78.08</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="F14">
         <v>42</v>
@@ -1558,24 +1529,24 @@
         <v>126</v>
       </c>
       <c r="I14">
-        <v>10386</v>
+        <v>10227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>96.47</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
       <c r="D15">
-        <v>1349.3</v>
+        <v>1391.3</v>
       </c>
       <c r="E15">
-        <v>79.17</v>
+        <v>79.94</v>
       </c>
       <c r="F15">
         <v>42</v>
@@ -1587,15 +1558,15 @@
         <v>126</v>
       </c>
       <c r="I15">
-        <v>10054</v>
+        <v>10070</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>97.58</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1604,7 +1575,7 @@
         <v>856.77</v>
       </c>
       <c r="E16">
-        <v>81.14</v>
+        <v>80.48</v>
       </c>
       <c r="F16">
         <v>42</v>
@@ -1616,24 +1587,24 @@
         <v>126</v>
       </c>
       <c r="I16">
-        <v>9895</v>
+        <v>9748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>95.7</v>
+        <v>96.16</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17">
-        <v>954.71</v>
+        <v>926</v>
       </c>
       <c r="E17">
-        <v>79.8</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="F17">
         <v>42</v>
@@ -1645,15 +1616,15 @@
         <v>126</v>
       </c>
       <c r="I17">
-        <v>9771</v>
+        <v>9788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>96.25</v>
+        <v>95.56</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1662,7 +1633,7 @@
         <v>1154.89</v>
       </c>
       <c r="E18">
-        <v>78.40000000000001</v>
+        <v>77.72</v>
       </c>
       <c r="F18">
         <v>42</v>
@@ -1674,15 +1645,15 @@
         <v>126</v>
       </c>
       <c r="I18">
-        <v>9692</v>
+        <v>9575</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>96.48999999999999</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -1691,7 +1662,7 @@
         <v>894.67</v>
       </c>
       <c r="E19">
-        <v>80.77</v>
+        <v>80.11</v>
       </c>
       <c r="F19">
         <v>42</v>
@@ -1703,15 +1674,15 @@
         <v>126</v>
       </c>
       <c r="I19">
-        <v>9561</v>
+        <v>9471</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>95.11</v>
+        <v>95.84</v>
       </c>
       <c r="C20">
         <v>6</v>
@@ -1720,7 +1691,7 @@
         <v>739.78</v>
       </c>
       <c r="E20">
-        <v>77.91</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="F20">
         <v>42</v>
@@ -1732,15 +1703,15 @@
         <v>126</v>
       </c>
       <c r="I20">
-        <v>9552</v>
+        <v>9557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>96.03</v>
+        <v>94.94</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -1749,7 +1720,7 @@
         <v>842</v>
       </c>
       <c r="E21">
-        <v>78.72</v>
+        <v>77.61</v>
       </c>
       <c r="F21">
         <v>42</v>
@@ -1761,15 +1732,15 @@
         <v>126</v>
       </c>
       <c r="I21">
-        <v>9369</v>
+        <v>9259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>95.88</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -1778,7 +1749,7 @@
         <v>882</v>
       </c>
       <c r="E22">
-        <v>79.18000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F22">
         <v>42</v>
@@ -1790,15 +1761,15 @@
         <v>126</v>
       </c>
       <c r="I22">
-        <v>9293</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>95.38</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -1807,7 +1778,7 @@
         <v>1028.35</v>
       </c>
       <c r="E23">
-        <v>78.31999999999999</v>
+        <v>77.33</v>
       </c>
       <c r="F23">
         <v>42</v>
@@ -1819,15 +1790,15 @@
         <v>126</v>
       </c>
       <c r="I23">
-        <v>9066</v>
+        <v>8935</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>95.28</v>
+        <v>96.36</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -1836,7 +1807,7 @@
         <v>897.45</v>
       </c>
       <c r="E24">
-        <v>77.86</v>
+        <v>78.62</v>
       </c>
       <c r="F24">
         <v>42</v>
@@ -1848,65 +1819,7 @@
         <v>126</v>
       </c>
       <c r="I24">
-        <v>9079</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>95.15000000000001</v>
-      </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25">
-        <v>782.75</v>
-      </c>
-      <c r="E25">
-        <v>77.73999999999999</v>
-      </c>
-      <c r="F25">
-        <v>42</v>
-      </c>
-      <c r="G25">
-        <v>84</v>
-      </c>
-      <c r="H25">
-        <v>126</v>
-      </c>
-      <c r="I25">
-        <v>8866</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>39.47</v>
-      </c>
-      <c r="C26">
-        <v>19.2</v>
-      </c>
-      <c r="D26">
-        <v>42</v>
-      </c>
-      <c r="E26">
-        <v>7.6</v>
-      </c>
-      <c r="F26">
-        <v>42</v>
-      </c>
-      <c r="G26">
-        <v>42</v>
-      </c>
-      <c r="H26">
-        <v>42</v>
-      </c>
-      <c r="I26">
-        <v>9</v>
+        <v>9150</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
@@ -407,28 +407,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>120.55</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1712.67</v>
+        <v>997.72</v>
       </c>
       <c r="E2">
-        <v>97.52</v>
+        <v>92.22</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>42</v>
       </c>
-      <c r="G2">
-        <v>84</v>
-      </c>
       <c r="H2">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I2">
-        <v>19110</v>
+        <v>18133</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +436,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>103.77</v>
+        <v>59.74</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1164.77</v>
+        <v>843.2</v>
       </c>
       <c r="E3">
-        <v>88.14</v>
+        <v>81.19</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>42</v>
       </c>
-      <c r="G3">
-        <v>84</v>
-      </c>
       <c r="H3">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>15773</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="4">
@@ -465,28 +465,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>105.04</v>
+        <v>58.61</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>1009.16</v>
       </c>
       <c r="E4">
-        <v>89</v>
+        <v>82.19</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>42</v>
       </c>
-      <c r="G4">
-        <v>84</v>
-      </c>
       <c r="H4">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>14724</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="5">
@@ -494,28 +494,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>99.3</v>
+        <v>52.48</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>1260</v>
       </c>
       <c r="E5">
-        <v>82.08</v>
+        <v>75.14</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>42</v>
       </c>
-      <c r="G5">
-        <v>84</v>
-      </c>
       <c r="H5">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>13502</v>
+        <v>14714</v>
       </c>
     </row>
     <row r="6">
@@ -523,28 +523,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>99.88</v>
+        <v>52.22</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>989.49</v>
+        <v>798</v>
       </c>
       <c r="E6">
-        <v>83.90000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>38.39</v>
       </c>
       <c r="H6">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>12822</v>
+        <v>14372</v>
       </c>
     </row>
     <row r="7">
@@ -552,28 +552,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>97.63</v>
+        <v>49.4</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1689.75</v>
+        <v>840</v>
       </c>
       <c r="E7">
-        <v>82.73999999999999</v>
+        <v>74</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H7">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>12157</v>
+        <v>14099</v>
       </c>
     </row>
     <row r="8">
@@ -581,28 +581,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>98.62</v>
+        <v>49.37</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1076.75</v>
+        <v>1058.37</v>
       </c>
       <c r="E8">
-        <v>82.65000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H8">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>11772</v>
+        <v>13856</v>
       </c>
     </row>
     <row r="9">
@@ -610,28 +610,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>94.98</v>
+        <v>45.92</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>798</v>
       </c>
       <c r="E9">
-        <v>77.83</v>
+        <v>70.12</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>126</v>
+        <v>80.39</v>
       </c>
       <c r="I9">
-        <v>11232</v>
+        <v>13637</v>
       </c>
     </row>
     <row r="10">
@@ -639,28 +639,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>97</v>
+        <v>48.03</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>782</v>
       </c>
       <c r="E10">
-        <v>80.83</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>11129</v>
+        <v>13467</v>
       </c>
     </row>
     <row r="11">
@@ -668,28 +668,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>96.3</v>
+        <v>47.1</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>718.5</v>
       </c>
       <c r="E11">
-        <v>78.39</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>10982</v>
+        <v>13293</v>
       </c>
     </row>
     <row r="12">
@@ -697,28 +697,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>94.7</v>
+        <v>45.74</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>1106.3</v>
       </c>
       <c r="E12">
-        <v>77.27</v>
+        <v>70.47</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>126</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="I12">
-        <v>10611</v>
+        <v>13148</v>
       </c>
     </row>
     <row r="13">
@@ -726,28 +726,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>97.68000000000001</v>
+        <v>47.85</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>1021.14</v>
       </c>
       <c r="E13">
-        <v>81.03</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I13">
-        <v>10692</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="14">
@@ -755,28 +755,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>95.45999999999999</v>
+        <v>46.06</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>853.1799999999999</v>
+        <v>672</v>
       </c>
       <c r="E14">
-        <v>77.20999999999999</v>
+        <v>70.11</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I14">
-        <v>10348</v>
+        <v>12827</v>
       </c>
     </row>
     <row r="15">
@@ -784,28 +784,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>97.31</v>
+        <v>46.19</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1391.3</v>
+        <v>752.39</v>
       </c>
       <c r="E15">
-        <v>80.09</v>
+        <v>70.98</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>126</v>
+        <v>80.39</v>
       </c>
       <c r="I15">
-        <v>10184</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="16">
@@ -813,28 +813,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>97.09</v>
+        <v>44.98</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>856.77</v>
+        <v>758</v>
       </c>
       <c r="E16">
-        <v>80.48</v>
+        <v>71.55</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I16">
-        <v>9852</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +842,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>96.18000000000001</v>
+        <v>44.95</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>926</v>
+        <v>699.5700000000001</v>
       </c>
       <c r="E17">
-        <v>80.34999999999999</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="F17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I17">
-        <v>9897</v>
+        <v>12416</v>
       </c>
     </row>
     <row r="18">
@@ -871,28 +871,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>95.67</v>
+        <v>43.84</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1154.89</v>
+        <v>588</v>
       </c>
       <c r="E18">
-        <v>77.97</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I18">
-        <v>9671</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="19">
@@ -900,28 +900,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>95.66</v>
+        <v>44.93</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>894.67</v>
+        <v>748.78</v>
       </c>
       <c r="E19">
-        <v>79.98</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I19">
-        <v>9573</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="20">
@@ -929,28 +929,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>95.86</v>
+        <v>45.17</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>739.78</v>
+        <v>730.75</v>
       </c>
       <c r="E20">
-        <v>78.77</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>126</v>
+        <v>73.72</v>
       </c>
       <c r="I20">
-        <v>9650</v>
+        <v>12053</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +958,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>95.11</v>
+        <v>43.24</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>842</v>
+        <v>798</v>
       </c>
       <c r="E21">
-        <v>77.63</v>
+        <v>68.55</v>
       </c>
       <c r="F21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I21">
-        <v>9355</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="22">
@@ -987,28 +987,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>96.93000000000001</v>
+        <v>44.98</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="E22">
-        <v>80.88</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F22">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I22">
-        <v>9422</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1016,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>94.76000000000001</v>
+        <v>42.66</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1028.35</v>
+        <v>840</v>
       </c>
       <c r="E23">
-        <v>77.31</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F23">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I23">
-        <v>9028</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1045,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>96.45</v>
+        <v>45.15</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>897.45</v>
+        <v>714</v>
       </c>
       <c r="E24">
-        <v>78.81</v>
+        <v>70.87</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I24">
-        <v>9230</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="25">
@@ -1074,28 +1074,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>94.22</v>
+        <v>42.12</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>756</v>
+        <v>733.2</v>
       </c>
       <c r="E25">
-        <v>76.54000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="F25">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I25">
-        <v>8767</v>
+        <v>7477</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1160,28 +1160,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>120.55</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1712.67</v>
+        <v>997.72</v>
       </c>
       <c r="E2">
-        <v>97.52</v>
+        <v>92.22</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>42</v>
       </c>
-      <c r="G2">
-        <v>84</v>
-      </c>
       <c r="H2">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I2">
-        <v>19110</v>
+        <v>18133</v>
       </c>
     </row>
     <row r="3">
@@ -1189,28 +1189,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>103.76</v>
+        <v>59.74</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1164.77</v>
+        <v>843.2</v>
       </c>
       <c r="E3">
-        <v>88.05</v>
+        <v>81.19</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>42</v>
       </c>
-      <c r="G3">
-        <v>84</v>
-      </c>
       <c r="H3">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I3">
-        <v>15561</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="4">
@@ -1218,28 +1218,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>105.03</v>
+        <v>58.61</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>1009.16</v>
       </c>
       <c r="E4">
-        <v>88.86</v>
+        <v>82.19</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>42</v>
       </c>
-      <c r="G4">
-        <v>84</v>
-      </c>
       <c r="H4">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I4">
-        <v>14529</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="5">
@@ -1247,28 +1247,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>99.69</v>
+        <v>52.48</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>1260</v>
       </c>
       <c r="E5">
-        <v>82.01000000000001</v>
+        <v>75.14</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>42</v>
       </c>
-      <c r="G5">
-        <v>84</v>
-      </c>
       <c r="H5">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>13125</v>
+        <v>14714</v>
       </c>
     </row>
     <row r="6">
@@ -1276,28 +1276,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>100.14</v>
+        <v>52.22</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>989.49</v>
+        <v>798</v>
       </c>
       <c r="E6">
-        <v>83.93000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>38.39</v>
       </c>
       <c r="H6">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>12545</v>
+        <v>14372</v>
       </c>
     </row>
     <row r="7">
@@ -1305,28 +1305,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>97.70999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1689.75</v>
+        <v>840</v>
       </c>
       <c r="E7">
-        <v>82.84999999999999</v>
+        <v>74</v>
       </c>
       <c r="F7">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H7">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>11939</v>
+        <v>14099</v>
       </c>
     </row>
     <row r="8">
@@ -1334,28 +1334,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>98.53</v>
+        <v>49.37</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1076.75</v>
+        <v>1058.37</v>
       </c>
       <c r="E8">
-        <v>82.51000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>19.2</v>
       </c>
       <c r="H8">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>11581</v>
+        <v>13856</v>
       </c>
     </row>
     <row r="9">
@@ -1363,28 +1363,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>94.94</v>
+        <v>45.92</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>798</v>
       </c>
       <c r="E9">
-        <v>77.76000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="F9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>126</v>
+        <v>80.39</v>
       </c>
       <c r="I9">
-        <v>11061</v>
+        <v>13637</v>
       </c>
     </row>
     <row r="10">
@@ -1392,28 +1392,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>97.02</v>
+        <v>48.03</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>782</v>
       </c>
       <c r="E10">
-        <v>80.95999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>10977</v>
+        <v>13467</v>
       </c>
     </row>
     <row r="11">
@@ -1421,28 +1421,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>96.42</v>
+        <v>47.1</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>718.5</v>
       </c>
       <c r="E11">
-        <v>78.45999999999999</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="F11">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>10839</v>
+        <v>13293</v>
       </c>
     </row>
     <row r="12">
@@ -1450,28 +1450,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>94.77</v>
+        <v>45.74</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>1106.3</v>
       </c>
       <c r="E12">
-        <v>77.23</v>
+        <v>70.47</v>
       </c>
       <c r="F12">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>126</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="I12">
-        <v>10496</v>
+        <v>13148</v>
       </c>
     </row>
     <row r="13">
@@ -1479,28 +1479,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>97.59</v>
+        <v>47.85</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>1021.14</v>
       </c>
       <c r="E13">
-        <v>80.81999999999999</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F13">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I13">
-        <v>10537</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="14">
@@ -1508,28 +1508,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>95.27</v>
+        <v>46.06</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>853.1799999999999</v>
+        <v>672</v>
       </c>
       <c r="E14">
-        <v>76.84999999999999</v>
+        <v>70.11</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="I14">
-        <v>10227</v>
+        <v>12827</v>
       </c>
     </row>
     <row r="15">
@@ -1537,28 +1537,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>97.23999999999999</v>
+        <v>46.19</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1391.3</v>
+        <v>752.39</v>
       </c>
       <c r="E15">
-        <v>79.94</v>
+        <v>70.98</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>126</v>
+        <v>80.39</v>
       </c>
       <c r="I15">
-        <v>10070</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="16">
@@ -1566,28 +1566,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>97</v>
+        <v>44.98</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>856.77</v>
+        <v>758</v>
       </c>
       <c r="E16">
-        <v>80.48</v>
+        <v>71.55</v>
       </c>
       <c r="F16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I16">
-        <v>9748</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1595,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>96.16</v>
+        <v>44.95</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>926</v>
+        <v>699.5700000000001</v>
       </c>
       <c r="E17">
-        <v>80.20999999999999</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="F17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I17">
-        <v>9788</v>
+        <v>12416</v>
       </c>
     </row>
     <row r="18">
@@ -1624,28 +1624,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>95.56</v>
+        <v>43.84</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1154.89</v>
+        <v>588</v>
       </c>
       <c r="E18">
-        <v>77.72</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F18">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I18">
-        <v>9575</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="19">
@@ -1653,28 +1653,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>95.73999999999999</v>
+        <v>44.93</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>894.67</v>
+        <v>748.78</v>
       </c>
       <c r="E19">
-        <v>80.11</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F19">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I19">
-        <v>9471</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="20">
@@ -1682,28 +1682,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>95.84</v>
+        <v>45.17</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>739.78</v>
+        <v>730.75</v>
       </c>
       <c r="E20">
-        <v>78.81999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="F20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>126</v>
+        <v>73.72</v>
       </c>
       <c r="I20">
-        <v>9557</v>
+        <v>12053</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +1711,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>94.94</v>
+        <v>43.24</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>842</v>
+        <v>798</v>
       </c>
       <c r="E21">
-        <v>77.61</v>
+        <v>68.55</v>
       </c>
       <c r="F21">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I21">
-        <v>9259</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="22">
@@ -1740,28 +1740,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>96.70999999999999</v>
+        <v>44.98</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>882</v>
       </c>
       <c r="E22">
-        <v>80.40000000000001</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F22">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I22">
-        <v>9327</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +1769,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>94.70999999999999</v>
+        <v>42.66</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1028.35</v>
+        <v>840</v>
       </c>
       <c r="E23">
-        <v>77.33</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F23">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>126</v>
+        <v>61.2</v>
       </c>
       <c r="I23">
-        <v>8935</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="24">
@@ -1798,28 +1798,57 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>96.36</v>
+        <v>45.15</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>897.45</v>
+        <v>714</v>
       </c>
       <c r="E24">
-        <v>78.62</v>
+        <v>70.87</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>126</v>
+        <v>68.75</v>
       </c>
       <c r="I24">
-        <v>9150</v>
+        <v>11550</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>42.12</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>733.2</v>
+      </c>
+      <c r="E25">
+        <v>67.38</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>61.2</v>
+      </c>
+      <c r="I25">
+        <v>7477</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>87.27</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1002.86</v>
+        <v>918.86</v>
       </c>
       <c r="E2">
-        <v>92.98999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="F2">
-        <v>26.75</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>57.59</v>
+        <v>80.39</v>
       </c>
       <c r="H2">
         <v>126</v>
       </c>
       <c r="I2">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J2">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="K2">
-        <v>85.88</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L2">
-        <v>88.65000000000001</v>
+        <v>94.91</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>60.41</v>
+        <v>65.8</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,7 +469,7 @@
         <v>835.74</v>
       </c>
       <c r="E3">
-        <v>79.58</v>
+        <v>83.59</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -481,16 +481,16 @@
         <v>84</v>
       </c>
       <c r="I3">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J3">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K3">
-        <v>59.23</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="L3">
-        <v>61.6</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -498,37 +498,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>52.39</v>
+        <v>60.29</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1009.16</v>
+        <v>1078.73</v>
       </c>
       <c r="E4">
-        <v>79.56</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="H4">
         <v>84</v>
       </c>
       <c r="I4">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J4">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K4">
-        <v>51.21</v>
+        <v>59.2</v>
       </c>
       <c r="L4">
-        <v>53.58</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>43.74</v>
+        <v>49.87</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -545,28 +545,28 @@
         <v>1182.9</v>
       </c>
       <c r="E5">
-        <v>71.65000000000001</v>
+        <v>74.47</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H5">
-        <v>61.2</v>
+        <v>84</v>
       </c>
       <c r="I5">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J5">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="K5">
-        <v>42.67</v>
+        <v>48.9</v>
       </c>
       <c r="L5">
-        <v>44.81</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>41.48</v>
+        <v>45.43</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -583,7 +583,7 @@
         <v>779.96</v>
       </c>
       <c r="E6">
-        <v>72.31999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>42</v>
+        <v>61.2</v>
       </c>
       <c r="I6">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J6">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="K6">
-        <v>40.4</v>
+        <v>44.46</v>
       </c>
       <c r="L6">
-        <v>42.56</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>37.86</v>
+        <v>40.6</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>840</v>
       </c>
       <c r="E7">
-        <v>68.62</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -633,16 +633,16 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J7">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="K7">
-        <v>36.84</v>
+        <v>39.69</v>
       </c>
       <c r="L7">
-        <v>38.89</v>
+        <v>41.52</v>
       </c>
     </row>
     <row r="8">
@@ -650,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>36.45</v>
+        <v>38.99</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>1102.65</v>
       </c>
       <c r="E8">
-        <v>68.79000000000001</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -671,16 +671,16 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J8">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="K8">
-        <v>35.43</v>
+        <v>38.07</v>
       </c>
       <c r="L8">
-        <v>37.48</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32.78</v>
+        <v>35.36</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>798</v>
+        <v>1214.24</v>
       </c>
       <c r="E9">
-        <v>63.54</v>
+        <v>65.58</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -709,16 +709,16 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J9">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="K9">
-        <v>31.83</v>
+        <v>34.5</v>
       </c>
       <c r="L9">
-        <v>33.73</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>32.99</v>
+        <v>34.98</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>64.73999999999999</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -747,16 +747,16 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J10">
-        <v>0.49</v>
+        <v>0.44</v>
       </c>
       <c r="K10">
-        <v>32.02</v>
+        <v>34.11</v>
       </c>
       <c r="L10">
-        <v>33.95</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>31.65</v>
+        <v>33.58</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>714</v>
+        <v>1466.24</v>
       </c>
       <c r="E11">
-        <v>62.83</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J11">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="K11">
-        <v>30.72</v>
+        <v>32.74</v>
       </c>
       <c r="L11">
-        <v>32.59</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>29.83</v>
+        <v>31.39</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1106.3</v>
+        <v>1580.75</v>
       </c>
       <c r="E12">
-        <v>61.66</v>
+        <v>63.18</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>42</v>
       </c>
       <c r="I12">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J12">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="K12">
-        <v>28.91</v>
+        <v>30.56</v>
       </c>
       <c r="L12">
-        <v>30.75</v>
+        <v>32.22</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>30.35</v>
+        <v>32.25</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1021.14</v>
+        <v>1324.98</v>
       </c>
       <c r="E13">
-        <v>63.37</v>
+        <v>65.27</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -861,16 +861,16 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J13">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="K13">
-        <v>29.4</v>
+        <v>31.39</v>
       </c>
       <c r="L13">
-        <v>31.29</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>28.09</v>
+        <v>29.63</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>630</v>
+        <v>853.14</v>
       </c>
       <c r="E14">
-        <v>59.41</v>
+        <v>60.66</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J14">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="K14">
-        <v>27.2</v>
+        <v>28.83</v>
       </c>
       <c r="L14">
-        <v>28.97</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="15">
@@ -916,7 +916,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>27.51</v>
+        <v>29.27</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>754.67</v>
       </c>
       <c r="E15">
-        <v>60.07</v>
+        <v>61.92</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J15">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="K15">
-        <v>26.62</v>
+        <v>28.46</v>
       </c>
       <c r="L15">
-        <v>28.41</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="16">
@@ -954,7 +954,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>26.09</v>
+        <v>27.75</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>758</v>
       </c>
       <c r="E16">
-        <v>59.59</v>
+        <v>60.83</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J16">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="K16">
-        <v>25.2</v>
+        <v>26.96</v>
       </c>
       <c r="L16">
-        <v>26.98</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="17">
@@ -992,7 +992,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>25.48</v>
+        <v>26.73</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1001,7 +1001,7 @@
         <v>680.37</v>
       </c>
       <c r="E17">
-        <v>58.48</v>
+        <v>59.51</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1010,19 +1010,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>38.39</v>
+        <v>42</v>
       </c>
       <c r="I17">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J17">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="K17">
-        <v>24.6</v>
+        <v>25.96</v>
       </c>
       <c r="L17">
-        <v>26.35</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>24.01</v>
+        <v>25.4</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>588</v>
+        <v>659.52</v>
       </c>
       <c r="E18">
-        <v>54.81</v>
+        <v>56.47</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1048,19 +1048,19 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>19.2</v>
+        <v>42</v>
       </c>
       <c r="I18">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J18">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="K18">
-        <v>23.19</v>
+        <v>24.66</v>
       </c>
       <c r="L18">
-        <v>24.83</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="19">
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>23.87</v>
+        <v>24.85</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>763.54</v>
       </c>
       <c r="E19">
-        <v>57.01</v>
+        <v>58.09</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>19.2</v>
       </c>
       <c r="I19">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J19">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="K19">
-        <v>23.02</v>
+        <v>24.09</v>
       </c>
       <c r="L19">
-        <v>24.72</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="20">
@@ -1106,7 +1106,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>23.01</v>
+        <v>24.52</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>730.75</v>
       </c>
       <c r="E20">
-        <v>55.57</v>
+        <v>57.43</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I20">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J20">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="K20">
-        <v>22.18</v>
+        <v>23.77</v>
       </c>
       <c r="L20">
-        <v>23.84</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="21">
@@ -1144,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>21.37</v>
+        <v>22.78</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>798</v>
       </c>
       <c r="E21">
-        <v>53.3</v>
+        <v>54.97</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J21">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="K21">
-        <v>20.58</v>
+        <v>22.06</v>
       </c>
       <c r="L21">
-        <v>22.16</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="22">
@@ -1182,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>22.13</v>
+        <v>23.34</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         <v>882</v>
       </c>
       <c r="E22">
-        <v>55.8</v>
+        <v>57.42</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1203,16 +1203,16 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J22">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="K22">
-        <v>21.3</v>
+        <v>22.58</v>
       </c>
       <c r="L22">
-        <v>22.96</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="23">
@@ -1220,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>19.99</v>
+        <v>21.14</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>840</v>
       </c>
       <c r="E23">
-        <v>51.58</v>
+        <v>53.07</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J23">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="K23">
-        <v>19.23</v>
+        <v>20.45</v>
       </c>
       <c r="L23">
-        <v>20.76</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="24">
@@ -1258,7 +1258,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>20.52</v>
+        <v>21.64</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>714</v>
       </c>
       <c r="E24">
-        <v>53.67</v>
+        <v>54.88</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J24">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
       <c r="K24">
-        <v>19.72</v>
+        <v>20.92</v>
       </c>
       <c r="L24">
-        <v>21.32</v>
+        <v>22.36</v>
       </c>
     </row>
     <row r="25">
@@ -1296,7 +1296,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>18.6</v>
+        <v>19.63</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>756</v>
       </c>
       <c r="E25">
-        <v>50.6</v>
+        <v>51.84</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J25">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="K25">
-        <v>17.85</v>
+        <v>18.95</v>
       </c>
       <c r="L25">
-        <v>19.35</v>
+        <v>20.31</v>
       </c>
     </row>
   </sheetData>
@@ -1406,37 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>99.65000000000001</v>
+        <v>107.84</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>966</v>
+        <v>888.84</v>
       </c>
       <c r="E2">
-        <v>86.81999999999999</v>
+        <v>89.91</v>
       </c>
       <c r="F2">
-        <v>26.75</v>
+        <v>38.39</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="H2">
         <v>126</v>
       </c>
       <c r="I2">
-        <v>17311</v>
+        <v>22407</v>
       </c>
       <c r="J2">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="K2">
-        <v>98.36</v>
+        <v>106.67</v>
       </c>
       <c r="L2">
-        <v>100.94</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="3">
@@ -1444,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>70.05</v>
+        <v>75.31</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>839.46</v>
       </c>
       <c r="E3">
-        <v>78.66</v>
+        <v>80.37</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1465,16 +1465,16 @@
         <v>84</v>
       </c>
       <c r="I3">
-        <v>16307</v>
+        <v>21922</v>
       </c>
       <c r="J3">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="K3">
-        <v>68.84</v>
+        <v>74.25</v>
       </c>
       <c r="L3">
-        <v>71.26000000000001</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="4">
@@ -1482,7 +1482,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>66.97</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1491,7 +1491,7 @@
         <v>1008</v>
       </c>
       <c r="E4">
-        <v>79.51000000000001</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>84</v>
       </c>
       <c r="I4">
-        <v>15083</v>
+        <v>21014</v>
       </c>
       <c r="J4">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K4">
-        <v>65.7</v>
+        <v>71.39</v>
       </c>
       <c r="L4">
-        <v>68.23999999999999</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="5">
@@ -1520,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>58.76</v>
+        <v>63.18</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1529,28 +1529,28 @@
         <v>741.86</v>
       </c>
       <c r="E5">
-        <v>72.97</v>
+        <v>74.53</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>38.39</v>
+        <v>42</v>
       </c>
       <c r="H5">
         <v>84</v>
       </c>
       <c r="I5">
-        <v>14470</v>
+        <v>19680</v>
       </c>
       <c r="J5">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="K5">
-        <v>57.57</v>
+        <v>62.14</v>
       </c>
       <c r="L5">
-        <v>59.95</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="6">
@@ -1558,37 +1558,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>56.6</v>
+        <v>60.75</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>740.7</v>
+        <v>839.46</v>
       </c>
       <c r="E6">
-        <v>73.78</v>
+        <v>74.23</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>26.75</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>84</v>
       </c>
       <c r="I6">
-        <v>14097</v>
+        <v>18513</v>
       </c>
       <c r="J6">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="K6">
-        <v>55.38</v>
+        <v>59.69</v>
       </c>
       <c r="L6">
-        <v>57.82</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="7">
@@ -1596,7 +1596,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.99</v>
+        <v>57.49</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1605,28 +1605,28 @@
         <v>840</v>
       </c>
       <c r="E7">
-        <v>70.81999999999999</v>
+        <v>72.38</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>19.2</v>
+        <v>38.39</v>
       </c>
       <c r="H7">
-        <v>76.78</v>
+        <v>84</v>
       </c>
       <c r="I7">
-        <v>13800</v>
+        <v>17683</v>
       </c>
       <c r="J7">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="K7">
-        <v>51.81</v>
+        <v>56.42</v>
       </c>
       <c r="L7">
-        <v>54.17</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="8">
@@ -1634,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>52.18</v>
+        <v>57.39</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1643,28 +1643,28 @@
         <v>1086.36</v>
       </c>
       <c r="E8">
-        <v>72.84</v>
+        <v>74.73</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>19.2</v>
+        <v>36.86</v>
       </c>
       <c r="H8">
-        <v>57.59</v>
+        <v>84</v>
       </c>
       <c r="I8">
-        <v>13542</v>
+        <v>17019</v>
       </c>
       <c r="J8">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="K8">
-        <v>50.95</v>
+        <v>56.26</v>
       </c>
       <c r="L8">
-        <v>53.41</v>
+        <v>58.51</v>
       </c>
     </row>
     <row r="9">
@@ -1672,37 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>47.23</v>
+        <v>53.73</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>798</v>
+        <v>1134</v>
       </c>
       <c r="E9">
-        <v>67.53</v>
+        <v>70.42</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>19.2</v>
+        <v>26.75</v>
       </c>
       <c r="H9">
-        <v>42</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I9">
-        <v>13317</v>
+        <v>16420</v>
       </c>
       <c r="J9">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="K9">
-        <v>46.09</v>
+        <v>52.66</v>
       </c>
       <c r="L9">
-        <v>48.38</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="10">
@@ -1710,37 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>48.67</v>
+        <v>55.15</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>714</v>
+        <v>1302</v>
       </c>
       <c r="E10">
-        <v>68.97</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H10">
-        <v>49.38</v>
+        <v>84</v>
       </c>
       <c r="I10">
-        <v>13129</v>
+        <v>15897</v>
       </c>
       <c r="J10">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="K10">
-        <v>47.49</v>
+        <v>54.03</v>
       </c>
       <c r="L10">
-        <v>49.85</v>
+        <v>56.27</v>
       </c>
     </row>
     <row r="11">
@@ -1748,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>47.17</v>
+        <v>54.76</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>714</v>
+        <v>1386</v>
       </c>
       <c r="E11">
-        <v>66.83</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H11">
-        <v>49.38</v>
+        <v>84</v>
       </c>
       <c r="I11">
-        <v>12954</v>
+        <v>15352</v>
       </c>
       <c r="J11">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="K11">
-        <v>46.02</v>
+        <v>53.64</v>
       </c>
       <c r="L11">
-        <v>48.32</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="12">
@@ -1786,37 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>45.28</v>
+        <v>52.8</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>641.9400000000001</v>
+        <v>1554</v>
       </c>
       <c r="E12">
-        <v>66.75</v>
+        <v>69.97</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H12">
-        <v>42</v>
+        <v>81.95</v>
       </c>
       <c r="I12">
-        <v>12806</v>
+        <v>14894</v>
       </c>
       <c r="J12">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="K12">
-        <v>44.12</v>
+        <v>51.67</v>
       </c>
       <c r="L12">
-        <v>46.43</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="13">
@@ -1824,37 +1824,37 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>46.19</v>
+        <v>55.67</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>840</v>
+        <v>1218</v>
       </c>
       <c r="E13">
-        <v>68.08</v>
+        <v>72.09</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I13">
-        <v>12663</v>
+        <v>14453</v>
       </c>
       <c r="J13">
         <v>0.6</v>
       </c>
       <c r="K13">
-        <v>45</v>
+        <v>54.49</v>
       </c>
       <c r="L13">
-        <v>47.37</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="14">
@@ -1862,37 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>43.58</v>
+        <v>52.93</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>691.3200000000001</v>
+        <v>756</v>
       </c>
       <c r="E14">
-        <v>64.5</v>
+        <v>67.92</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H14">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I14">
-        <v>12487</v>
+        <v>13971</v>
       </c>
       <c r="J14">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="K14">
-        <v>42.45</v>
+        <v>51.8</v>
       </c>
       <c r="L14">
-        <v>44.71</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="15">
@@ -1900,7 +1900,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>43.39</v>
+        <v>54.23</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1909,28 +1909,28 @@
         <v>790.08</v>
       </c>
       <c r="E15">
-        <v>66.89</v>
+        <v>70.98</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="H15">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I15">
-        <v>12349</v>
+        <v>13573</v>
       </c>
       <c r="J15">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="K15">
-        <v>42.21</v>
+        <v>53.04</v>
       </c>
       <c r="L15">
-        <v>44.57</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="16">
@@ -1938,7 +1938,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>41.82</v>
+        <v>53.39</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1947,28 +1947,28 @@
         <v>740.7</v>
       </c>
       <c r="E16">
-        <v>66.87</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H16">
-        <v>42</v>
+        <v>76.78</v>
       </c>
       <c r="I16">
-        <v>12208</v>
+        <v>13156</v>
       </c>
       <c r="J16">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="K16">
-        <v>40.64</v>
+        <v>52.17</v>
       </c>
       <c r="L16">
-        <v>43.01</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="17">
@@ -1976,7 +1976,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>40.96</v>
+        <v>52.78</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1985,28 +1985,28 @@
         <v>592.5599999999999</v>
       </c>
       <c r="E17">
-        <v>66.26000000000001</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H17">
-        <v>42</v>
+        <v>57.59</v>
       </c>
       <c r="I17">
-        <v>12079</v>
+        <v>12733</v>
       </c>
       <c r="J17">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="K17">
-        <v>39.78</v>
+        <v>51.55</v>
       </c>
       <c r="L17">
-        <v>42.14</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="18">
@@ -2014,37 +2014,37 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>38.51</v>
+        <v>51.35</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>588</v>
+        <v>740.7</v>
       </c>
       <c r="E18">
-        <v>61.61</v>
+        <v>67.38</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H18">
-        <v>42</v>
+        <v>75.38</v>
       </c>
       <c r="I18">
-        <v>11953</v>
+        <v>12334</v>
       </c>
       <c r="J18">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="K18">
-        <v>37.4</v>
+        <v>50.16</v>
       </c>
       <c r="L18">
-        <v>39.61</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="19">
@@ -2052,7 +2052,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>39.21</v>
+        <v>52.11</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2061,28 +2061,28 @@
         <v>790.08</v>
       </c>
       <c r="E19">
-        <v>65.56</v>
+        <v>71.11</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H19">
-        <v>42</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I19">
-        <v>11830</v>
+        <v>11979</v>
       </c>
       <c r="J19">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="K19">
-        <v>38.02</v>
+        <v>50.84</v>
       </c>
       <c r="L19">
-        <v>40.39</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="20">
@@ -2090,37 +2090,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>37.67</v>
+        <v>52.73</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>641.9400000000001</v>
+        <v>790.08</v>
       </c>
       <c r="E20">
-        <v>62.85</v>
+        <v>70.39</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H20">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I20">
-        <v>11716</v>
+        <v>11635</v>
       </c>
       <c r="J20">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="K20">
-        <v>36.53</v>
+        <v>51.45</v>
       </c>
       <c r="L20">
-        <v>38.81</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="21">
@@ -2128,7 +2128,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>35.67</v>
+        <v>50.49</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2137,28 +2137,28 @@
         <v>839.46</v>
       </c>
       <c r="E21">
-        <v>62.27</v>
+        <v>69.37</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H21">
-        <v>42</v>
+        <v>49.38</v>
       </c>
       <c r="I21">
-        <v>11600</v>
+        <v>11288</v>
       </c>
       <c r="J21">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="K21">
-        <v>34.53</v>
+        <v>49.21</v>
       </c>
       <c r="L21">
-        <v>36.8</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="22">
@@ -2166,37 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>37.57</v>
+        <v>53.81</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="E22">
-        <v>64.68000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H22">
-        <v>42</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I22">
-        <v>11474</v>
+        <v>10919</v>
       </c>
       <c r="J22">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K22">
-        <v>36.39</v>
+        <v>52.45</v>
       </c>
       <c r="L22">
-        <v>38.76</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="23">
@@ -2204,37 +2204,37 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>33.98</v>
+        <v>50.02</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>641.9400000000001</v>
+        <v>714</v>
       </c>
       <c r="E23">
-        <v>59.98</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H23">
-        <v>42</v>
+        <v>57.59</v>
       </c>
       <c r="I23">
-        <v>11335</v>
+        <v>10562</v>
       </c>
       <c r="J23">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="K23">
-        <v>32.88</v>
+        <v>48.72</v>
       </c>
       <c r="L23">
-        <v>35.09</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="24">
@@ -2242,7 +2242,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>35.53</v>
+        <v>53.24</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2251,28 +2251,28 @@
         <v>714</v>
       </c>
       <c r="E24">
-        <v>62.57</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="H24">
-        <v>42</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="I24">
-        <v>11221</v>
+        <v>10215</v>
       </c>
       <c r="J24">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="K24">
-        <v>34.37</v>
+        <v>51.86</v>
       </c>
       <c r="L24">
-        <v>36.68</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="25">
@@ -2280,7 +2280,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>33.8</v>
+        <v>51.65</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2289,28 +2289,28 @@
         <v>855.1900000000001</v>
       </c>
       <c r="E25">
-        <v>62.01</v>
+        <v>70.73</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>19.56</v>
       </c>
       <c r="H25">
-        <v>42.79</v>
+        <v>58.67</v>
       </c>
       <c r="I25">
-        <v>11098</v>
+        <v>9900</v>
       </c>
       <c r="J25">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="K25">
-        <v>32.65</v>
+        <v>50.25</v>
       </c>
       <c r="L25">
-        <v>34.95</v>
+        <v>53.04</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_costs_Raw.xlsx
@@ -422,37 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>93.65000000000001</v>
+        <v>143.71</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>918.86</v>
+        <v>2747.01</v>
       </c>
       <c r="E2">
-        <v>95.92</v>
+        <v>188.51</v>
       </c>
       <c r="F2">
         <v>42</v>
       </c>
       <c r="G2">
-        <v>80.39</v>
+        <v>86.55</v>
       </c>
       <c r="H2">
-        <v>126</v>
+        <v>179.98</v>
       </c>
       <c r="I2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J2">
-        <v>0.64</v>
+        <v>1.26</v>
       </c>
       <c r="K2">
-        <v>92.40000000000001</v>
+        <v>141.25</v>
       </c>
       <c r="L2">
-        <v>94.91</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="3">
@@ -460,37 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>65.8</v>
+        <v>98.22</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>835.74</v>
+        <v>2375.88</v>
       </c>
       <c r="E3">
-        <v>83.59</v>
+        <v>157.92</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>44.55</v>
       </c>
       <c r="H3">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="I3">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J3">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="K3">
-        <v>64.70999999999999</v>
+        <v>96.16</v>
       </c>
       <c r="L3">
-        <v>66.90000000000001</v>
+        <v>100.29</v>
       </c>
     </row>
     <row r="4">
@@ -498,16 +498,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>60.29</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1078.73</v>
+        <v>3002.89</v>
       </c>
       <c r="E4">
-        <v>83.34999999999999</v>
+        <v>159.83</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -516,19 +516,19 @@
         <v>42</v>
       </c>
       <c r="H4">
-        <v>84</v>
+        <v>108.37</v>
       </c>
       <c r="I4">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J4">
-        <v>0.5600000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="K4">
-        <v>59.2</v>
+        <v>88.67</v>
       </c>
       <c r="L4">
-        <v>61.38</v>
+        <v>92.84999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -536,37 +536,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>49.87</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1182.9</v>
+        <v>2625.08</v>
       </c>
       <c r="E5">
-        <v>74.47</v>
+        <v>139.9</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>19.2</v>
+        <v>21.83</v>
       </c>
       <c r="H5">
-        <v>84</v>
+        <v>86.55</v>
       </c>
       <c r="I5">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>0.93</v>
       </c>
       <c r="K5">
-        <v>48.9</v>
+        <v>72.91</v>
       </c>
       <c r="L5">
-        <v>50.85</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -574,37 +574,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>45.43</v>
+        <v>67.12</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>779.96</v>
+        <v>2051.65</v>
       </c>
       <c r="E6">
-        <v>73.7</v>
+        <v>131.33</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="H6">
-        <v>61.2</v>
+        <v>84</v>
       </c>
       <c r="I6">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J6">
-        <v>0.49</v>
+        <v>0.88</v>
       </c>
       <c r="K6">
-        <v>44.46</v>
+        <v>65.41</v>
       </c>
       <c r="L6">
-        <v>46.39</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="7">
@@ -612,37 +612,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>40.6</v>
+        <v>60.35</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>840</v>
+        <v>2415.81</v>
       </c>
       <c r="E7">
-        <v>69.79000000000001</v>
+        <v>126.97</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="H7">
-        <v>42</v>
+        <v>63.74</v>
       </c>
       <c r="I7">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J7">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="K7">
-        <v>39.69</v>
+        <v>58.69</v>
       </c>
       <c r="L7">
-        <v>41.52</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="8">
@@ -650,37 +650,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>38.99</v>
+        <v>58.25</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1102.65</v>
+        <v>3244.49</v>
       </c>
       <c r="E8">
-        <v>70.68000000000001</v>
+        <v>131.52</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="H8">
-        <v>42</v>
+        <v>53.72</v>
       </c>
       <c r="I8">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J8">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
       <c r="K8">
-        <v>38.07</v>
+        <v>56.53</v>
       </c>
       <c r="L8">
-        <v>39.92</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>35.36</v>
+        <v>52.74</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1214.24</v>
+        <v>3352.55</v>
       </c>
       <c r="E9">
-        <v>65.58</v>
+        <v>118.83</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -706,19 +706,19 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>42</v>
+        <v>47.09</v>
       </c>
       <c r="I9">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J9">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="K9">
-        <v>34.5</v>
+        <v>51.19</v>
       </c>
       <c r="L9">
-        <v>36.22</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>34.98</v>
+        <v>51.85</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>2289.1</v>
       </c>
       <c r="E10">
-        <v>66.48999999999999</v>
+        <v>119.67</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -744,19 +744,19 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>42</v>
+        <v>45.82</v>
       </c>
       <c r="I10">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J10">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="K10">
-        <v>34.11</v>
+        <v>50.29</v>
       </c>
       <c r="L10">
-        <v>35.85</v>
+        <v>53.42</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>33.58</v>
+        <v>50.43</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1466.24</v>
+        <v>2677.22</v>
       </c>
       <c r="E11">
-        <v>64.48999999999999</v>
+        <v>116.96</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -782,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>42</v>
+        <v>44.55</v>
       </c>
       <c r="I11">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J11">
-        <v>0.43</v>
+        <v>0.78</v>
       </c>
       <c r="K11">
-        <v>32.74</v>
+        <v>48.9</v>
       </c>
       <c r="L11">
-        <v>34.42</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>31.39</v>
+        <v>46.81</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1580.75</v>
+        <v>2943.78</v>
       </c>
       <c r="E12">
-        <v>63.18</v>
+        <v>115.7</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -820,19 +820,19 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>42</v>
+        <v>43.27</v>
       </c>
       <c r="I12">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J12">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="K12">
-        <v>30.56</v>
+        <v>45.3</v>
       </c>
       <c r="L12">
-        <v>32.22</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>32.25</v>
+        <v>48.38</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1324.98</v>
+        <v>2693.9</v>
       </c>
       <c r="E13">
-        <v>65.27</v>
+        <v>119.3</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -858,19 +858,19 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>42</v>
+        <v>43.27</v>
       </c>
       <c r="I13">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J13">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="K13">
-        <v>31.39</v>
+        <v>46.82</v>
       </c>
       <c r="L13">
-        <v>33.1</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>29.63</v>
+        <v>43.92</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>853.14</v>
+        <v>3499.21</v>
       </c>
       <c r="E14">
-        <v>60.66</v>
+        <v>110.03</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J14">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="K14">
-        <v>28.83</v>
+        <v>42.48</v>
       </c>
       <c r="L14">
-        <v>30.42</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="15">
@@ -916,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>29.27</v>
+        <v>43.77</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>754.67</v>
+        <v>1933.41</v>
       </c>
       <c r="E15">
-        <v>61.92</v>
+        <v>110.42</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J15">
-        <v>0.41</v>
+        <v>0.74</v>
       </c>
       <c r="K15">
-        <v>28.46</v>
+        <v>42.33</v>
       </c>
       <c r="L15">
-        <v>30.08</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="16">
@@ -954,16 +954,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>27.75</v>
+        <v>41.85</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>758</v>
+        <v>2422.28</v>
       </c>
       <c r="E16">
-        <v>60.83</v>
+        <v>111.4</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J16">
-        <v>0.41</v>
+        <v>0.74</v>
       </c>
       <c r="K16">
-        <v>26.96</v>
+        <v>40.39</v>
       </c>
       <c r="L16">
-        <v>28.55</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="17">
@@ -992,16 +992,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>26.73</v>
+        <v>39.94</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>680.37</v>
+        <v>2027.58</v>
       </c>
       <c r="E17">
-        <v>59.51</v>
+        <v>107.38</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1013,16 +1013,16 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J17">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="K17">
-        <v>25.96</v>
+        <v>38.54</v>
       </c>
       <c r="L17">
-        <v>27.51</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>25.4</v>
+        <v>37.98</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>659.52</v>
+        <v>1738.77</v>
       </c>
       <c r="E18">
-        <v>56.47</v>
+        <v>100.97</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1051,16 +1051,16 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J18">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="K18">
-        <v>24.66</v>
+        <v>36.65</v>
       </c>
       <c r="L18">
-        <v>26.14</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="19">
@@ -1068,16 +1068,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>24.85</v>
+        <v>37.23</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>763.54</v>
+        <v>2386.48</v>
       </c>
       <c r="E19">
-        <v>58.09</v>
+        <v>105.27</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>19.2</v>
+        <v>26.75</v>
       </c>
       <c r="I19">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J19">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="K19">
-        <v>24.09</v>
+        <v>35.85</v>
       </c>
       <c r="L19">
-        <v>25.61</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="20">
@@ -1106,16 +1106,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>24.52</v>
+        <v>37.03</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>730.75</v>
+        <v>2469.89</v>
       </c>
       <c r="E20">
-        <v>57.43</v>
+        <v>104.71</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1127,16 +1127,16 @@
         <v>19.2</v>
       </c>
       <c r="I20">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J20">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="K20">
-        <v>23.77</v>
+        <v>35.67</v>
       </c>
       <c r="L20">
-        <v>25.27</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="21">
@@ -1144,16 +1144,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22.78</v>
+        <v>34.17</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>798</v>
+        <v>2544.3</v>
       </c>
       <c r="E21">
-        <v>54.97</v>
+        <v>101.7</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>7.81</v>
       </c>
       <c r="I21">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J21">
-        <v>0.37</v>
+        <v>0.68</v>
       </c>
       <c r="K21">
-        <v>22.06</v>
+        <v>32.84</v>
       </c>
       <c r="L21">
-        <v>23.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="22">
@@ -1182,16 +1182,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>23.34</v>
+        <v>35.36</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>882</v>
+        <v>2832.41</v>
       </c>
       <c r="E22">
-        <v>57.42</v>
+        <v>106.34</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1200,19 +1200,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="I22">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J22">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="K22">
-        <v>22.58</v>
+        <v>33.97</v>
       </c>
       <c r="L22">
-        <v>24.09</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="23">
@@ -1220,16 +1220,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>21.14</v>
+        <v>32.01</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>840</v>
+        <v>2528.79</v>
       </c>
       <c r="E23">
-        <v>53.07</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1238,19 +1238,19 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="I23">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J23">
-        <v>0.35</v>
+        <v>0.65</v>
       </c>
       <c r="K23">
-        <v>20.45</v>
+        <v>30.73</v>
       </c>
       <c r="L23">
-        <v>21.84</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="24">
@@ -1258,16 +1258,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>21.64</v>
+        <v>32.33</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>714</v>
+        <v>1973.01</v>
       </c>
       <c r="E24">
-        <v>54.88</v>
+        <v>97.06</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1276,19 +1276,19 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="I24">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J24">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="K24">
-        <v>20.92</v>
+        <v>31.06</v>
       </c>
       <c r="L24">
-        <v>22.36</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="25">
@@ -1296,16 +1296,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>19.63</v>
+        <v>30.45</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>756</v>
+        <v>2751.93</v>
       </c>
       <c r="E25">
-        <v>51.84</v>
+        <v>98.78</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1314,19 +1314,19 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="I25">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J25">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="K25">
-        <v>18.95</v>
+        <v>29.16</v>
       </c>
       <c r="L25">
-        <v>20.31</v>
+        <v>31.74</v>
       </c>
     </row>
   </sheetData>
@@ -1406,37 +1406,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>107.84</v>
+        <v>135.4</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>888.84</v>
+        <v>1848</v>
       </c>
       <c r="E2">
-        <v>89.91</v>
+        <v>120.44</v>
       </c>
       <c r="F2">
-        <v>38.39</v>
+        <v>19.2</v>
       </c>
       <c r="G2">
-        <v>49.38</v>
+        <v>42</v>
       </c>
       <c r="H2">
         <v>126</v>
       </c>
       <c r="I2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K2">
-        <v>106.67</v>
+        <v>133.82</v>
       </c>
       <c r="L2">
-        <v>109.02</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="3">
@@ -1444,16 +1444,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>75.31</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>839.46</v>
+        <v>1176</v>
       </c>
       <c r="E3">
-        <v>80.37</v>
+        <v>106.85</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1465,16 +1465,16 @@
         <v>84</v>
       </c>
       <c r="I3">
-        <v>21922</v>
+        <v>21973</v>
       </c>
       <c r="J3">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="K3">
-        <v>74.25</v>
+        <v>94.41</v>
       </c>
       <c r="L3">
-        <v>76.37</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1482,16 +1482,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>72.48999999999999</v>
+        <v>93.05</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1008</v>
+        <v>1932</v>
       </c>
       <c r="E4">
-        <v>80.98999999999999</v>
+        <v>108.79</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1503,16 +1503,16 @@
         <v>84</v>
       </c>
       <c r="I4">
-        <v>21014</v>
+        <v>21056</v>
       </c>
       <c r="J4">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="K4">
-        <v>71.39</v>
+        <v>91.58</v>
       </c>
       <c r="L4">
-        <v>73.58</v>
+        <v>94.52</v>
       </c>
     </row>
     <row r="5">
@@ -1520,16 +1520,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>63.18</v>
+        <v>81.27</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>741.86</v>
+        <v>1411.9</v>
       </c>
       <c r="E5">
-        <v>74.53</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1541,16 +1541,16 @@
         <v>84</v>
       </c>
       <c r="I5">
-        <v>19680</v>
+        <v>19708</v>
       </c>
       <c r="J5">
-        <v>0.53</v>
+        <v>0.7</v>
       </c>
       <c r="K5">
-        <v>62.14</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L5">
-        <v>64.22</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1558,16 +1558,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>60.75</v>
+        <v>78.27</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>839.46</v>
+        <v>1344</v>
       </c>
       <c r="E6">
-        <v>74.23</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>84</v>
       </c>
       <c r="I6">
-        <v>18513</v>
+        <v>18537</v>
       </c>
       <c r="J6">
-        <v>0.55</v>
+        <v>0.71</v>
       </c>
       <c r="K6">
-        <v>59.69</v>
+        <v>76.88</v>
       </c>
       <c r="L6">
-        <v>61.82</v>
+        <v>79.66</v>
       </c>
     </row>
     <row r="7">
@@ -1596,16 +1596,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>57.49</v>
+        <v>73.89</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>840</v>
+        <v>1134</v>
       </c>
       <c r="E7">
-        <v>72.38</v>
+        <v>94.75</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         <v>84</v>
       </c>
       <c r="I7">
-        <v>17683</v>
+        <v>17706</v>
       </c>
       <c r="J7">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="K7">
-        <v>56.42</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="L7">
-        <v>58.55</v>
+        <v>75.28</v>
       </c>
     </row>
     <row r="8">
@@ -1634,37 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>57.39</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1086.36</v>
+        <v>1629.54</v>
       </c>
       <c r="E8">
-        <v>74.73</v>
+        <v>100.12</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>36.86</v>
+        <v>38.39</v>
       </c>
       <c r="H8">
         <v>84</v>
       </c>
       <c r="I8">
-        <v>17019</v>
+        <v>17039</v>
       </c>
       <c r="J8">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="K8">
-        <v>56.26</v>
+        <v>72.75</v>
       </c>
       <c r="L8">
-        <v>58.51</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1672,16 +1672,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>53.73</v>
+        <v>69.83</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1134</v>
+        <v>1764</v>
       </c>
       <c r="E9">
-        <v>70.42</v>
+        <v>94.5</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1690,19 +1690,19 @@
         <v>26.75</v>
       </c>
       <c r="H9">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I9">
-        <v>16420</v>
+        <v>16440</v>
       </c>
       <c r="J9">
-        <v>0.55</v>
+        <v>0.74</v>
       </c>
       <c r="K9">
-        <v>52.66</v>
+        <v>68.38</v>
       </c>
       <c r="L9">
-        <v>54.81</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="10">
@@ -1710,16 +1710,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>55.15</v>
+        <v>70.8</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1302</v>
+        <v>1386</v>
       </c>
       <c r="E10">
-        <v>71.95999999999999</v>
+        <v>93.92</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1731,16 +1731,16 @@
         <v>84</v>
       </c>
       <c r="I10">
-        <v>15897</v>
+        <v>15916</v>
       </c>
       <c r="J10">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="K10">
-        <v>54.03</v>
+        <v>69.34</v>
       </c>
       <c r="L10">
-        <v>56.27</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1748,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>54.76</v>
+        <v>71.39</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1386</v>
+        <v>1554</v>
       </c>
       <c r="E11">
-        <v>70.29000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>26.75</v>
+        <v>29.23</v>
       </c>
       <c r="H11">
         <v>84</v>
       </c>
       <c r="I11">
-        <v>15352</v>
+        <v>15368</v>
       </c>
       <c r="J11">
-        <v>0.57</v>
+        <v>0.74</v>
       </c>
       <c r="K11">
-        <v>53.64</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L11">
-        <v>55.87</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1786,16 +1786,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>52.8</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1554</v>
+        <v>1974</v>
       </c>
       <c r="E12">
-        <v>69.97</v>
+        <v>93.48</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1804,19 +1804,19 @@
         <v>19.2</v>
       </c>
       <c r="H12">
-        <v>81.95</v>
+        <v>84</v>
       </c>
       <c r="I12">
-        <v>14894</v>
+        <v>14910</v>
       </c>
       <c r="J12">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="K12">
-        <v>51.67</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="L12">
-        <v>53.92</v>
+        <v>69.76000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1824,16 +1824,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>55.67</v>
+        <v>72.61</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1218</v>
+        <v>1848</v>
       </c>
       <c r="E13">
-        <v>72.09</v>
+        <v>96.48</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1845,16 +1845,16 @@
         <v>84</v>
       </c>
       <c r="I13">
-        <v>14453</v>
+        <v>14467</v>
       </c>
       <c r="J13">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K13">
-        <v>54.49</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="L13">
-        <v>56.84</v>
+        <v>74.18000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1862,16 +1862,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>52.93</v>
+        <v>68.48</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>756</v>
+        <v>1428</v>
       </c>
       <c r="E14">
-        <v>67.92</v>
+        <v>90.81</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1883,16 +1883,16 @@
         <v>84</v>
       </c>
       <c r="I14">
-        <v>13971</v>
+        <v>13984</v>
       </c>
       <c r="J14">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="K14">
-        <v>51.8</v>
+        <v>66.98</v>
       </c>
       <c r="L14">
-        <v>54.06</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1900,16 +1900,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>54.23</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>790.08</v>
+        <v>1163.17</v>
       </c>
       <c r="E15">
-        <v>70.98</v>
+        <v>92.58</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>84</v>
       </c>
       <c r="I15">
-        <v>13573</v>
+        <v>13586</v>
       </c>
       <c r="J15">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="K15">
-        <v>53.04</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="L15">
-        <v>55.43</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="16">
@@ -1938,16 +1938,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>53.39</v>
+        <v>69.31</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>740.7</v>
+        <v>1386</v>
       </c>
       <c r="E16">
-        <v>71.43000000000001</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1956,19 +1956,19 @@
         <v>19.2</v>
       </c>
       <c r="H16">
-        <v>76.78</v>
+        <v>84</v>
       </c>
       <c r="I16">
-        <v>13156</v>
+        <v>13168</v>
       </c>
       <c r="J16">
-        <v>0.62</v>
+        <v>0.83</v>
       </c>
       <c r="K16">
-        <v>52.17</v>
+        <v>67.69</v>
       </c>
       <c r="L16">
-        <v>54.61</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="17">
@@ -1976,16 +1976,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>52.78</v>
+        <v>68.13</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>592.5599999999999</v>
+        <v>1092</v>
       </c>
       <c r="E17">
-        <v>71.01000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1994,19 +1994,19 @@
         <v>19.2</v>
       </c>
       <c r="H17">
-        <v>57.59</v>
+        <v>84</v>
       </c>
       <c r="I17">
-        <v>12733</v>
+        <v>12743</v>
       </c>
       <c r="J17">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="K17">
-        <v>51.55</v>
+        <v>66.52</v>
       </c>
       <c r="L17">
-        <v>54.01</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -2014,16 +2014,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>51.35</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>740.7</v>
+        <v>1302</v>
       </c>
       <c r="E18">
-        <v>67.38</v>
+        <v>89.88</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2032,19 +2032,19 @@
         <v>19.2</v>
       </c>
       <c r="H18">
-        <v>75.38</v>
+        <v>84</v>
       </c>
       <c r="I18">
-        <v>12334</v>
+        <v>12343</v>
       </c>
       <c r="J18">
-        <v>0.61</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K18">
-        <v>50.16</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="L18">
-        <v>52.54</v>
+        <v>68.52</v>
       </c>
     </row>
     <row r="19">
@@ -2052,16 +2052,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>52.11</v>
+        <v>67.47</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>790.08</v>
+        <v>1234.5</v>
       </c>
       <c r="E19">
-        <v>71.11</v>
+        <v>92.83</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2070,19 +2070,19 @@
         <v>19.2</v>
       </c>
       <c r="H19">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I19">
-        <v>11979</v>
+        <v>11988</v>
       </c>
       <c r="J19">
-        <v>0.65</v>
+        <v>0.85</v>
       </c>
       <c r="K19">
-        <v>50.84</v>
+        <v>65.81</v>
       </c>
       <c r="L19">
-        <v>53.39</v>
+        <v>69.13</v>
       </c>
     </row>
     <row r="20">
@@ -2090,16 +2090,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>52.73</v>
+        <v>69.25</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>790.08</v>
+        <v>1333.26</v>
       </c>
       <c r="E20">
-        <v>70.39</v>
+        <v>94.39</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2111,16 +2111,16 @@
         <v>84</v>
       </c>
       <c r="I20">
-        <v>11635</v>
+        <v>11643</v>
       </c>
       <c r="J20">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="K20">
-        <v>51.45</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="L20">
-        <v>54.01</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="21">
@@ -2128,16 +2128,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>50.49</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>839.46</v>
+        <v>1554</v>
       </c>
       <c r="E21">
-        <v>69.37</v>
+        <v>92.42</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2146,19 +2146,19 @@
         <v>19.2</v>
       </c>
       <c r="H21">
-        <v>49.38</v>
+        <v>76.78</v>
       </c>
       <c r="I21">
-        <v>11288</v>
+        <v>11294</v>
       </c>
       <c r="J21">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="K21">
-        <v>49.21</v>
+        <v>64.14</v>
       </c>
       <c r="L21">
-        <v>51.77</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="22">
@@ -2166,16 +2166,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>53.81</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>798</v>
+        <v>1382.64</v>
       </c>
       <c r="E22">
-        <v>72.73999999999999</v>
+        <v>97.94</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2184,19 +2184,19 @@
         <v>19.2</v>
       </c>
       <c r="H22">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I22">
-        <v>10919</v>
+        <v>10925</v>
       </c>
       <c r="J22">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K22">
-        <v>52.45</v>
+        <v>68.62</v>
       </c>
       <c r="L22">
-        <v>55.18</v>
+        <v>72.29000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2204,16 +2204,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>50.02</v>
+        <v>65.92</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>714</v>
+        <v>1428</v>
       </c>
       <c r="E23">
-        <v>68.01000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2222,19 +2222,19 @@
         <v>19.2</v>
       </c>
       <c r="H23">
-        <v>57.59</v>
+        <v>76.78</v>
       </c>
       <c r="I23">
-        <v>10562</v>
+        <v>10568</v>
       </c>
       <c r="J23">
-        <v>0.66</v>
+        <v>0.91</v>
       </c>
       <c r="K23">
-        <v>48.72</v>
+        <v>64.13</v>
       </c>
       <c r="L23">
-        <v>51.32</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2242,16 +2242,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>53.24</v>
+        <v>68.89</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>714</v>
+        <v>1117.21</v>
       </c>
       <c r="E24">
-        <v>70.84999999999999</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2260,19 +2260,19 @@
         <v>19.2</v>
       </c>
       <c r="H24">
-        <v>80.23999999999999</v>
+        <v>84</v>
       </c>
       <c r="I24">
-        <v>10215</v>
+        <v>10221</v>
       </c>
       <c r="J24">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="K24">
-        <v>51.86</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L24">
-        <v>54.61</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="25">
@@ -2280,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>51.65</v>
+        <v>68.41</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>855.1900000000001</v>
+        <v>1509.16</v>
       </c>
       <c r="E25">
-        <v>70.73</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2298,19 +2298,19 @@
         <v>19.56</v>
       </c>
       <c r="H25">
-        <v>58.67</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="I25">
-        <v>9900</v>
+        <v>9906</v>
       </c>
       <c r="J25">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="K25">
-        <v>50.25</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="L25">
-        <v>53.04</v>
+        <v>70.34</v>
       </c>
     </row>
   </sheetData>
